--- a/result/LOOCV/SVR/without_41/nBA/1&2_nBA_SVR_LOOCV_mechanism_oriented_perc=40_without_41.xlsx
+++ b/result/LOOCV/SVR/without_41/nBA/1&2_nBA_SVR_LOOCV_mechanism_oriented_perc=40_without_41.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8576754082028387</v>
+        <v>0.8522682602576751</v>
       </c>
       <c r="C2" t="n">
-        <v>1.891236319671248</v>
+        <v>1.86901908373619</v>
       </c>
       <c r="D2" t="n">
         <v>2.45</v>
@@ -468,7 +468,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9292414966249675</v>
+        <v>0.9292414966249676</v>
       </c>
       <c r="C3" t="n">
         <v>1.765510165941099</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9564615828171127</v>
+        <v>0.9564615828171125</v>
       </c>
       <c r="C4" t="n">
-        <v>1.896094392796249</v>
+        <v>1.89609439279625</v>
       </c>
       <c r="D4" t="n">
         <v>2.05</v>
@@ -503,7 +503,7 @@
         <v>0.8860063906659643</v>
       </c>
       <c r="C5" t="n">
-        <v>2.116963701972287</v>
+        <v>2.116963701972282</v>
       </c>
       <c r="D5" t="n">
         <v>1.9</v>
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9301612847842107</v>
+        <v>0.9301612847842105</v>
       </c>
       <c r="C6" t="n">
         <v>2.032319400203713</v>
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9134498160485397</v>
+        <v>0.91344981604854</v>
       </c>
       <c r="C7" t="n">
-        <v>1.564834725725463</v>
+        <v>1.564834725725462</v>
       </c>
       <c r="D7" t="n">
         <v>1.44</v>
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9456924895013724</v>
+        <v>0.9456924895013725</v>
       </c>
       <c r="C8" t="n">
         <v>1.988613570994308</v>
@@ -564,10 +564,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9301219891172815</v>
+        <v>0.9301219891172814</v>
       </c>
       <c r="C9" t="n">
-        <v>2.782322965854788</v>
+        <v>2.782322965854785</v>
       </c>
       <c r="D9" t="n">
         <v>2.25</v>
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9336628074744417</v>
+        <v>0.9481913941165798</v>
       </c>
       <c r="C10" t="n">
-        <v>1.593769547660082</v>
+        <v>1.651195868581452</v>
       </c>
       <c r="D10" t="n">
         <v>1.75</v>
@@ -596,10 +596,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6059190695213205</v>
+        <v>0.6511501499201692</v>
       </c>
       <c r="C11" t="n">
-        <v>2.651426452718415</v>
+        <v>3.097811864602302</v>
       </c>
       <c r="D11" t="n">
         <v>3.81</v>
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9121139869065893</v>
+        <v>0.912113986906589</v>
       </c>
       <c r="C13" t="n">
         <v>1.556345199464247</v>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9193864722484817</v>
+        <v>0.9193864722484825</v>
       </c>
       <c r="C14" t="n">
         <v>1.442971511282391</v>
@@ -663,7 +663,7 @@
         <v>0.8358527600771796</v>
       </c>
       <c r="C15" t="n">
-        <v>1.595417850252569</v>
+        <v>1.595417850252567</v>
       </c>
       <c r="D15" t="n">
         <v>1.5</v>
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9174147801004296</v>
+        <v>0.9174147801004303</v>
       </c>
       <c r="C16" t="n">
         <v>1.337145587960421</v>
@@ -692,10 +692,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7480387660677363</v>
+        <v>0.7480387660677361</v>
       </c>
       <c r="C17" t="n">
-        <v>2.82818752061558</v>
+        <v>2.828187520615586</v>
       </c>
       <c r="D17" t="n">
         <v>2.8</v>
@@ -708,10 +708,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8117673423584584</v>
+        <v>0.8315312513176547</v>
       </c>
       <c r="C18" t="n">
-        <v>2.846217142369086</v>
+        <v>2.750880591390795</v>
       </c>
       <c r="D18" t="n">
         <v>1.95</v>
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9119447648315009</v>
+        <v>0.9119447648315011</v>
       </c>
       <c r="C19" t="n">
         <v>1.632012528888971</v>
